--- a/Proyecto Interno/interno/02_dataprep/eer/output/230726_agg_eer.xlsx
+++ b/Proyecto Interno/interno/02_dataprep/eer/output/230726_agg_eer.xlsx
@@ -2733,7 +2733,7 @@
         </is>
       </c>
       <c r="D119">
-        <v>3001.939185407725</v>
+        <v>3003.637134916764</v>
       </c>
     </row>
     <row r="120">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="D120">
-        <v>2916.948023795984</v>
+        <v>2920.96351356654</v>
       </c>
     </row>
     <row r="121">
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="D131">
-        <v>2180.239498110854</v>
+        <v>2183.354796224263</v>
       </c>
     </row>
     <row r="132">
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="D133">
-        <v>2139.834041003507</v>
+        <v>2141.111895428849</v>
       </c>
     </row>
     <row r="134">
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="D135">
-        <v>2970.907424535481</v>
+        <v>2981.025640443366</v>
       </c>
     </row>
     <row r="136">
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="D136">
-        <v>2871.237836532005</v>
+        <v>2872.508188603007</v>
       </c>
     </row>
     <row r="137">
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="D139">
-        <v>2205.851272927871</v>
+        <v>2208.210509585895</v>
       </c>
     </row>
     <row r="140">
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="D154">
-        <v>2164.636347397608</v>
+        <v>2164.765748539002</v>
       </c>
     </row>
     <row r="155">
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="D155">
-        <v>2190.366089545558</v>
+        <v>2190.750659641264</v>
       </c>
     </row>
     <row r="156">
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="D156">
-        <v>2135.511960788058</v>
+        <v>2135.763319282007</v>
       </c>
     </row>
     <row r="157">
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="D157">
-        <v>2018.567974145908</v>
+        <v>2015.63372277661</v>
       </c>
     </row>
     <row r="158">
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="D158">
-        <v>2950.529735466498</v>
+        <v>1889.811285321821</v>
       </c>
     </row>
     <row r="159">
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="D159">
-        <v>2715.120222853123</v>
+        <v>2715.490179738342</v>
       </c>
     </row>
     <row r="160">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="D160">
-        <v>2960.769680205883</v>
+        <v>2960.151960571723</v>
       </c>
     </row>
     <row r="161">
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="D161">
-        <v>2865.87250579842</v>
+        <v>2866.422054661984</v>
       </c>
     </row>
     <row r="162">
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="D162">
-        <v>2673.685046165263</v>
+        <v>2672.691765751979</v>
       </c>
     </row>
     <row r="163">
@@ -3613,7 +3613,7 @@
         </is>
       </c>
       <c r="D163">
-        <v>2979.15880215902</v>
+        <v>2266.415538210625</v>
       </c>
     </row>
     <row r="164">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="D165">
-        <v>2180.239498110854</v>
+        <v>2183.354796224263</v>
       </c>
     </row>
     <row r="166">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="D167">
-        <v>2139.834041003507</v>
+        <v>2141.111895428849</v>
       </c>
     </row>
     <row r="168">
@@ -3733,7 +3733,7 @@
         </is>
       </c>
       <c r="D169">
-        <v>2970.907424535481</v>
+        <v>2981.025640443366</v>
       </c>
     </row>
     <row r="170">
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="D170">
-        <v>2871.237836532005</v>
+        <v>2872.508188603007</v>
       </c>
     </row>
     <row r="171">
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="D173">
-        <v>2199.297999935925</v>
+        <v>2199.749073471314</v>
       </c>
     </row>
     <row r="174">
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="D174">
-        <v>2119.055130937514</v>
+        <v>2119.41557008015</v>
       </c>
     </row>
     <row r="175">
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="D176">
-        <v>2726.477511489837</v>
+        <v>2731.722651473469</v>
       </c>
     </row>
     <row r="177">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="D178">
-        <v>2843.367027154383</v>
+        <v>2844.776598159585</v>
       </c>
     </row>
     <row r="179">
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="D186">
-        <v>2825.993980336962</v>
+        <v>2826.158308781556</v>
       </c>
     </row>
     <row r="187">
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="D190">
-        <v>2125.872203914811</v>
+        <v>2126.54366271806</v>
       </c>
     </row>
     <row r="191">
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="D191">
-        <v>2006.27391414929</v>
+        <v>2007.112368139724</v>
       </c>
     </row>
     <row r="192">
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="D193">
-        <v>3002.784043973877</v>
+        <v>2986.545525377957</v>
       </c>
     </row>
     <row r="194">
@@ -4273,7 +4273,7 @@
         </is>
       </c>
       <c r="D196">
-        <v>2159.954584968008</v>
+        <v>2160.93827824352</v>
       </c>
     </row>
     <row r="197">
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="D197">
-        <v>2314.446783621303</v>
+        <v>2314.357079218158</v>
       </c>
     </row>
     <row r="198">
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="D198">
-        <v>2287.940578017411</v>
+        <v>2288.697918425905</v>
       </c>
     </row>
     <row r="199">
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="D202">
-        <v>2860.175463255805</v>
+        <v>2861.110921599867</v>
       </c>
     </row>
     <row r="203">
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="D203">
-        <v>2639.519083619814</v>
+        <v>2640.33353636871</v>
       </c>
     </row>
     <row r="204">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="D206">
-        <v>2079.65880769009</v>
+        <v>2079.769441757435</v>
       </c>
     </row>
     <row r="207">
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="D210">
-        <v>2764.688789269463</v>
+        <v>2765.974038917659</v>
       </c>
     </row>
     <row r="211">
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="D218">
-        <v>2825.993980336962</v>
+        <v>2826.158308781556</v>
       </c>
     </row>
     <row r="219">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="D220">
-        <v>2134.821024739233</v>
+        <v>2135.387703688431</v>
       </c>
     </row>
     <row r="221">
@@ -4793,7 +4793,7 @@
         </is>
       </c>
       <c r="D222">
-        <v>2118.686454214096</v>
+        <v>2118.740983903219</v>
       </c>
     </row>
     <row r="223">
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="D223">
-        <v>1967.268058476599</v>
+        <v>1967.689197842258</v>
       </c>
     </row>
     <row r="224">
